--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALETHIA LUCIA</t>
-  </si>
-  <si>
-    <t>FABIOLA</t>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
   </si>
 </sst>
 </file>
@@ -515,10 +506,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -527,7 +518,7 @@
         <v>77.14</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -580,16 +571,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.23</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -603,16 +597,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.56999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -668,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>74.36</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,19 +688,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -745,16 +742,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920245</v>
+        <v>20330051920234</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -763,30 +760,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920250</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
@@ -73,13 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
   </si>
 </sst>
 </file>
@@ -571,19 +571,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>69.23</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -665,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>79.48999999999999</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>88.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920234</v>
+        <v>20330051920228</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,19 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -710,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -748,10 +757,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -760,6 +769,29 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>
